--- a/evaluate.xlsx
+++ b/evaluate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\projects\ACOPF-feasible\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BECE43E-B64E-4216-916B-9BD2025C29D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2CB51E-6ACC-4C2C-850F-5B01872F801C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,37 +18,390 @@
     <sheet name="162" sheetId="3" r:id="rId3"/>
     <sheet name="300" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="7">
-  <si>
-    <t>Methods</t>
-  </si>
-  <si>
-    <t>Obj. Value</t>
-  </si>
-  <si>
-    <t>Max Eq.</t>
-  </si>
-  <si>
-    <t>Mean Eq.</t>
-  </si>
-  <si>
-    <t>Max Ineq.</t>
-  </si>
-  <si>
-    <t>Mean Ineq.</t>
-  </si>
-  <si>
-    <t>Time (s)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="121">
+  <si>
+    <t>Architecture</t>
+  </si>
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>Obj. Error (%)</t>
+  </si>
+  <si>
+    <t>Max_Eq</t>
+  </si>
+  <si>
+    <t>Mean_Eq</t>
+  </si>
+  <si>
+    <t>Max_Ineq</t>
+  </si>
+  <si>
+    <t>Mean_Ineq</t>
+  </si>
+  <si>
+    <t>MAE_v</t>
+  </si>
+  <si>
+    <t>MAE_pg</t>
+  </si>
+  <si>
+    <t>MAE_qg</t>
+  </si>
+  <si>
+    <t>Time_s</t>
+  </si>
+  <si>
+    <t>PINN Baseline</t>
+  </si>
+  <si>
+    <t>Run 1</t>
+  </si>
+  <si>
+    <t>0.76 (3.19)</t>
+  </si>
+  <si>
+    <t>Run 2</t>
+  </si>
+  <si>
+    <t>35.22 (3.20)</t>
+  </si>
+  <si>
+    <t>Run 3</t>
+  </si>
+  <si>
+    <t>32.89 (3.15)</t>
+  </si>
+  <si>
+    <t>Run 4</t>
+  </si>
+  <si>
+    <t>-19.24 (1.93)</t>
+  </si>
+  <si>
+    <t>Run 5</t>
+  </si>
+  <si>
+    <t>8.17 (2.69)</t>
+  </si>
+  <si>
+    <t>DC3</t>
+  </si>
+  <si>
+    <t>-38.74 (1.45)</t>
+  </si>
+  <si>
+    <t>-32.66 (1.61)</t>
+  </si>
+  <si>
+    <t>-31.81 (1.62)</t>
+  </si>
+  <si>
+    <t>-32.96 (1.67)</t>
+  </si>
+  <si>
+    <t>-36.82 (1.55)</t>
+  </si>
+  <si>
+    <t>FSNet</t>
+  </si>
+  <si>
+    <t>-9.68 (2.15)</t>
+  </si>
+  <si>
+    <t>-1.40 (3.26)</t>
+  </si>
+  <si>
+    <t>-1.39 (3.27)</t>
+  </si>
+  <si>
+    <t>-1.39 (3.28)</t>
+  </si>
+  <si>
+    <t>-1.40 (3.27)</t>
+  </si>
+  <si>
+    <t>KKT</t>
+  </si>
+  <si>
+    <t>6.02 (3.27)</t>
+  </si>
+  <si>
+    <t>6.08 (3.25)</t>
+  </si>
+  <si>
+    <t>6.18 (3.27)</t>
+  </si>
+  <si>
+    <t>5.97 (3.27)</t>
+  </si>
+  <si>
+    <t>6.04 (3.26)</t>
+  </si>
+  <si>
+    <t>Rahul's Model</t>
+  </si>
+  <si>
+    <t>9.34 (2.61)</t>
+  </si>
+  <si>
+    <t>11.68 (2.66)</t>
+  </si>
+  <si>
+    <t>6.25 (2.52)</t>
+  </si>
+  <si>
+    <t>9.26 (2.61)</t>
+  </si>
+  <si>
+    <t>10.12 (2.63)</t>
+  </si>
+  <si>
+    <t>-21.57 (2.65)</t>
+  </si>
+  <si>
+    <t>-21.60 (2.65)</t>
+  </si>
+  <si>
+    <t>-21.44 (2.66)</t>
+  </si>
+  <si>
+    <t>-21.42 (2.66)</t>
+  </si>
+  <si>
+    <t>-21.37 (2.62)</t>
+  </si>
+  <si>
+    <t>-21.90 (2.68)</t>
+  </si>
+  <si>
+    <t>-21.73 (2.66)</t>
+  </si>
+  <si>
+    <t>-21.75 (2.67)</t>
+  </si>
+  <si>
+    <t>-22.31 (2.63)</t>
+  </si>
+  <si>
+    <t>-21.96 (2.66)</t>
+  </si>
+  <si>
+    <t>-23.75 (2.64)</t>
+  </si>
+  <si>
+    <t>-23.88 (2.66)</t>
+  </si>
+  <si>
+    <t>-23.80 (2.65)</t>
+  </si>
+  <si>
+    <t>-23.85 (2.66)</t>
+  </si>
+  <si>
+    <t>-23.61 (2.66)</t>
+  </si>
+  <si>
+    <t>-18.52 (2.72)</t>
+  </si>
+  <si>
+    <t>-18.24 (2.73)</t>
+  </si>
+  <si>
+    <t>-18.57 (2.68)</t>
+  </si>
+  <si>
+    <t>-18.42 (2.69)</t>
+  </si>
+  <si>
+    <t>-18.50 (2.67)</t>
+  </si>
+  <si>
+    <t>8.54 (2.31)</t>
+  </si>
+  <si>
+    <t>9.40 (2.33)</t>
+  </si>
+  <si>
+    <t>7.42 (2.28)</t>
+  </si>
+  <si>
+    <t>12.54 (2.40)</t>
+  </si>
+  <si>
+    <t>8.96 (2.32)</t>
+  </si>
+  <si>
+    <t>517.82 (11.95)</t>
+  </si>
+  <si>
+    <t>543.47 (12.45)</t>
+  </si>
+  <si>
+    <t>568.33 (12.93)</t>
+  </si>
+  <si>
+    <t>531.77 (12.22)</t>
+  </si>
+  <si>
+    <t>529.48 (12.18)</t>
+  </si>
+  <si>
+    <t>516.51 (11.93)</t>
+  </si>
+  <si>
+    <t>521.19 (12.02)</t>
+  </si>
+  <si>
+    <t>520.88 (12.01)</t>
+  </si>
+  <si>
+    <t>522.77 (12.05)</t>
+  </si>
+  <si>
+    <t>520.91 (12.01)</t>
+  </si>
+  <si>
+    <t>500.87 (11.62)</t>
+  </si>
+  <si>
+    <t>502.11 (11.65)</t>
+  </si>
+  <si>
+    <t>504.39 (11.69)</t>
+  </si>
+  <si>
+    <t>505.22 (11.71)</t>
+  </si>
+  <si>
+    <t>501.63 (11.64)</t>
+  </si>
+  <si>
+    <t>507.23 (11.75)</t>
+  </si>
+  <si>
+    <t>520.19 (12.00)</t>
+  </si>
+  <si>
+    <t>507.47 (11.75)</t>
+  </si>
+  <si>
+    <t>538.26 (12.35)</t>
+  </si>
+  <si>
+    <t>508.94 (11.78)</t>
+  </si>
+  <si>
+    <t>1476.18 (30.48)</t>
+  </si>
+  <si>
+    <t>1474.20 (30.45)</t>
+  </si>
+  <si>
+    <t>1462.25 (30.22)</t>
+  </si>
+  <si>
+    <t>1473.26 (30.43)</t>
+  </si>
+  <si>
+    <t>1467.56 (30.35)</t>
+  </si>
+  <si>
+    <t>-37.51 (1.15)</t>
+  </si>
+  <si>
+    <t>-37.68 (1.19)</t>
+  </si>
+  <si>
+    <t>-40.97 (0.80)</t>
+  </si>
+  <si>
+    <t>-36.80 (1.28)</t>
+  </si>
+  <si>
+    <t>-42.86 (0.68)</t>
+  </si>
+  <si>
+    <t>-32.15 (1.03)</t>
+  </si>
+  <si>
+    <t>-31.94 (1.04)</t>
+  </si>
+  <si>
+    <t>-32.20 (0.97)</t>
+  </si>
+  <si>
+    <t>-32.07 (0.90)</t>
+  </si>
+  <si>
+    <t>-32.13 (0.77)</t>
+  </si>
+  <si>
+    <t>-34.47 (1.27)</t>
+  </si>
+  <si>
+    <t>-34.42 (1.33)</t>
+  </si>
+  <si>
+    <t>-34.32 (1.07)</t>
+  </si>
+  <si>
+    <t>-34.46 (1.29)</t>
+  </si>
+  <si>
+    <t>-34.47 (1.28)</t>
+  </si>
+  <si>
+    <t>-34.49 (1.42)</t>
+  </si>
+  <si>
+    <t>-34.17 (0.46)</t>
+  </si>
+  <si>
+    <t>-34.40 (1.11)</t>
+  </si>
+  <si>
+    <t>-34.99 (1.35)</t>
+  </si>
+  <si>
+    <t>-34.41 (0.34)</t>
+  </si>
+  <si>
+    <t>-8.20 (0.08)</t>
+  </si>
+  <si>
+    <t>-7.00 (0.06)</t>
+  </si>
+  <si>
+    <t>-7.62 (0.19)</t>
+  </si>
+  <si>
+    <t>-6.24 (0.30)</t>
+  </si>
+  <si>
+    <t>-8.77 (0.09)</t>
   </si>
 </sst>
 </file>
@@ -366,10 +719,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -390,6 +750,893 @@
       </c>
       <c r="G1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>1.6212730407714839</v>
+      </c>
+      <c r="E2">
+        <v>0.1203370690345764</v>
+      </c>
+      <c r="F2">
+        <v>0.18665981292724609</v>
+      </c>
+      <c r="G2">
+        <v>8.7264114990830421E-3</v>
+      </c>
+      <c r="H2">
+        <v>1.1772334575653081</v>
+      </c>
+      <c r="I2">
+        <v>1.4442285522818571E-2</v>
+      </c>
+      <c r="J2">
+        <v>6.6847771406173706E-2</v>
+      </c>
+      <c r="K2">
+        <v>9.7478999996383206E-6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3">
+        <v>1.116897821426392</v>
+      </c>
+      <c r="E3">
+        <v>0.12531702220439911</v>
+      </c>
+      <c r="F3">
+        <v>0.4395032525062561</v>
+      </c>
+      <c r="G3">
+        <v>3.9968475699424737E-2</v>
+      </c>
+      <c r="H3">
+        <v>0.1991908848285675</v>
+      </c>
+      <c r="I3">
+        <v>0.25246047973632813</v>
+      </c>
+      <c r="J3">
+        <v>7.2207406163215637E-2</v>
+      </c>
+      <c r="K3">
+        <v>4.6304999996209519E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4">
+        <v>1.161139249801636</v>
+      </c>
+      <c r="E4">
+        <v>0.11509360373020169</v>
+      </c>
+      <c r="F4">
+        <v>0.4398343563079834</v>
+      </c>
+      <c r="G4">
+        <v>4.1110429912805557E-2</v>
+      </c>
+      <c r="H4">
+        <v>0.19577403366565699</v>
+      </c>
+      <c r="I4">
+        <v>0.26128792762756348</v>
+      </c>
+      <c r="J4">
+        <v>7.2439767420291901E-2</v>
+      </c>
+      <c r="K4">
+        <v>4.9923000005946964E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>0.72234177589416504</v>
+      </c>
+      <c r="E5">
+        <v>0.11896944046020511</v>
+      </c>
+      <c r="F5">
+        <v>0.72148919105529785</v>
+      </c>
+      <c r="G5">
+        <v>7.0703312754631042E-2</v>
+      </c>
+      <c r="H5">
+        <v>0.93041056394577026</v>
+      </c>
+      <c r="I5">
+        <v>0.39839506149291992</v>
+      </c>
+      <c r="J5">
+        <v>5.048612505197525E-2</v>
+      </c>
+      <c r="K5">
+        <v>4.7004000007291327E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6">
+        <v>0.10727487504482271</v>
+      </c>
+      <c r="E6">
+        <v>4.4082868844270713E-2</v>
+      </c>
+      <c r="F6">
+        <v>7.4615955352783203E-2</v>
+      </c>
+      <c r="G6">
+        <v>1.0484969243407249E-3</v>
+      </c>
+      <c r="H6">
+        <v>1.187484502792358</v>
+      </c>
+      <c r="I6">
+        <v>0.42009776830673218</v>
+      </c>
+      <c r="J6">
+        <v>7.2793669998645782E-2</v>
+      </c>
+      <c r="K6">
+        <v>5.0539000003482212E-6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>0.99314618110656738</v>
+      </c>
+      <c r="E7">
+        <v>0.1250759959220886</v>
+      </c>
+      <c r="F7">
+        <v>7.9633831977844238E-2</v>
+      </c>
+      <c r="G7">
+        <v>4.2290529236197472E-3</v>
+      </c>
+      <c r="H7">
+        <v>9.4412609934806824E-2</v>
+      </c>
+      <c r="I7">
+        <v>0.21319752931594849</v>
+      </c>
+      <c r="J7">
+        <v>8.5281558334827423E-2</v>
+      </c>
+      <c r="K7">
+        <v>5.0980999985768004E-6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8">
+        <v>1.0535967350006099</v>
+      </c>
+      <c r="E8">
+        <v>0.11422099173069</v>
+      </c>
+      <c r="F8">
+        <v>3.4720242023468018E-2</v>
+      </c>
+      <c r="G8">
+        <v>1.8261234799865631E-4</v>
+      </c>
+      <c r="H8">
+        <v>7.6778285205364227E-2</v>
+      </c>
+      <c r="I8">
+        <v>0.17964209616184229</v>
+      </c>
+      <c r="J8">
+        <v>9.5510587096214294E-2</v>
+      </c>
+      <c r="K8">
+        <v>5.3234000006341377E-6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9">
+        <v>1.0686647891998291</v>
+      </c>
+      <c r="E9">
+        <v>0.11340101808309561</v>
+      </c>
+      <c r="F9">
+        <v>1.9898295402526859E-2</v>
+      </c>
+      <c r="G9">
+        <v>9.6150251920334995E-5</v>
+      </c>
+      <c r="H9">
+        <v>7.4276559054851532E-2</v>
+      </c>
+      <c r="I9">
+        <v>0.1749274730682373</v>
+      </c>
+      <c r="J9">
+        <v>9.153081476688385E-2</v>
+      </c>
+      <c r="K9">
+        <v>5.2174999982526062E-6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10">
+        <v>1.07895839214325</v>
+      </c>
+      <c r="E10">
+        <v>0.11527117341756821</v>
+      </c>
+      <c r="F10">
+        <v>4.3277084827423103E-2</v>
+      </c>
+      <c r="G10">
+        <v>5.5072753457352519E-4</v>
+      </c>
+      <c r="H10">
+        <v>1.159277677536011</v>
+      </c>
+      <c r="I10">
+        <v>0.18127751350402829</v>
+      </c>
+      <c r="J10">
+        <v>9.2141345143318176E-2</v>
+      </c>
+      <c r="K10">
+        <v>4.7819999999774157E-6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11">
+        <v>1.06371545791626</v>
+      </c>
+      <c r="E11">
+        <v>0.1208392605185509</v>
+      </c>
+      <c r="F11">
+        <v>6.3352584838867188E-2</v>
+      </c>
+      <c r="G11">
+        <v>2.0501208491623402E-3</v>
+      </c>
+      <c r="H11">
+        <v>8.4022156894207001E-2</v>
+      </c>
+      <c r="I11">
+        <v>0.20260909199714661</v>
+      </c>
+      <c r="J11">
+        <v>0.11582872271537779</v>
+      </c>
+      <c r="K11">
+        <v>5.1076000017928893E-6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12">
+        <v>1.434185385704041</v>
+      </c>
+      <c r="E12">
+        <v>0.26996293663978582</v>
+      </c>
+      <c r="F12">
+        <v>0.88189208507537842</v>
+      </c>
+      <c r="G12">
+        <v>9.6219189465045929E-2</v>
+      </c>
+      <c r="H12">
+        <v>0.61524254083633423</v>
+      </c>
+      <c r="I12">
+        <v>0.28614071011543268</v>
+      </c>
+      <c r="J12">
+        <v>0.11359900236129759</v>
+      </c>
+      <c r="K12">
+        <v>4.653399999369867E-6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13">
+        <v>9.6425561904907227</v>
+      </c>
+      <c r="E13">
+        <v>1.864211440086365</v>
+      </c>
+      <c r="F13">
+        <v>19.417173385620121</v>
+      </c>
+      <c r="G13">
+        <v>0.44676503539085388</v>
+      </c>
+      <c r="H13">
+        <v>0.40471658110618591</v>
+      </c>
+      <c r="I13">
+        <v>1.5731252729892731E-2</v>
+      </c>
+      <c r="J13">
+        <v>3.7323273718357093E-2</v>
+      </c>
+      <c r="K13">
+        <v>5.395099997258512E-6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14">
+        <v>9.7669696807861328</v>
+      </c>
+      <c r="E14">
+        <v>1.8744325637817381</v>
+      </c>
+      <c r="F14">
+        <v>20.11959266662598</v>
+      </c>
+      <c r="G14">
+        <v>0.45302087068557739</v>
+      </c>
+      <c r="H14">
+        <v>0.40666893124580378</v>
+      </c>
+      <c r="I14">
+        <v>1.5766950324177739E-2</v>
+      </c>
+      <c r="J14">
+        <v>3.7164784967899323E-2</v>
+      </c>
+      <c r="K14">
+        <v>4.9658000025374354E-6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15">
+        <v>9.5086688995361328</v>
+      </c>
+      <c r="E15">
+        <v>1.847036600112915</v>
+      </c>
+      <c r="F15">
+        <v>17.189302444458011</v>
+      </c>
+      <c r="G15">
+        <v>0.52363693714141846</v>
+      </c>
+      <c r="H15">
+        <v>0.37389984726905823</v>
+      </c>
+      <c r="I15">
+        <v>1.578175276517868E-2</v>
+      </c>
+      <c r="J15">
+        <v>3.9892815053462982E-2</v>
+      </c>
+      <c r="K15">
+        <v>4.9451000013505096E-6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16">
+        <v>9.4949178695678711</v>
+      </c>
+      <c r="E16">
+        <v>1.861482620239258</v>
+      </c>
+      <c r="F16">
+        <v>17.303726196289059</v>
+      </c>
+      <c r="G16">
+        <v>0.5127214789390564</v>
+      </c>
+      <c r="H16">
+        <v>0.37490770220756531</v>
+      </c>
+      <c r="I16">
+        <v>1.578537188470364E-2</v>
+      </c>
+      <c r="J16">
+        <v>3.7475232034921653E-2</v>
+      </c>
+      <c r="K16">
+        <v>5.0150999995821634E-6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17">
+        <v>1.769737720489502</v>
+      </c>
+      <c r="E17">
+        <v>0.19103994965553281</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>6.5188705921173096E-2</v>
+      </c>
+      <c r="I17">
+        <v>3.3143080770969391E-2</v>
+      </c>
+      <c r="J17">
+        <v>5.9852659702301032E-2</v>
+      </c>
+      <c r="K17">
+        <v>5.8996000007027758E-6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18">
+        <v>1.1792118549346919</v>
+      </c>
+      <c r="E18">
+        <v>0.18169532716274259</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>6.4474925398826599E-2</v>
+      </c>
+      <c r="I18">
+        <v>3.346049040555954E-2</v>
+      </c>
+      <c r="J18">
+        <v>6.4278088510036469E-2</v>
+      </c>
+      <c r="K18">
+        <v>6.0799999992013913E-6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19">
+        <v>2.229702472686768</v>
+      </c>
+      <c r="E19">
+        <v>0.20221211016178131</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>6.5306738018989563E-2</v>
+      </c>
+      <c r="I19">
+        <v>3.3953446894884109E-2</v>
+      </c>
+      <c r="J19">
+        <v>6.141677126288414E-2</v>
+      </c>
+      <c r="K19">
+        <v>6.4076000016939357E-6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20">
+        <v>1.57392954826355</v>
+      </c>
+      <c r="E20">
+        <v>0.17982649803161621</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>6.4832523465156555E-2</v>
+      </c>
+      <c r="I20">
+        <v>3.2897345721721649E-2</v>
+      </c>
+      <c r="J20">
+        <v>5.9747163206338882E-2</v>
+      </c>
+      <c r="K20">
+        <v>6.1230999999679634E-6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21">
+        <v>5.3038501739501953</v>
+      </c>
+      <c r="E21">
+        <v>0.47438862919807429</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0.20213201642036441</v>
+      </c>
+      <c r="I21">
+        <v>3.3242154866456992E-2</v>
+      </c>
+      <c r="J21">
+        <v>6.1229292303323753E-2</v>
+      </c>
+      <c r="K21">
+        <v>5.8202000000164847E-6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22">
+        <v>0.2656935453414917</v>
+      </c>
+      <c r="E22">
+        <v>6.1279676854610443E-2</v>
+      </c>
+      <c r="F22">
+        <v>2.9824614524841309E-2</v>
+      </c>
+      <c r="G22">
+        <v>6.7056715488433838E-4</v>
+      </c>
+      <c r="H22">
+        <v>6.2999919056892395E-2</v>
+      </c>
+      <c r="I22">
+        <v>0.41235098242759699</v>
+      </c>
+      <c r="J22">
+        <v>4.7242414206266403E-2</v>
+      </c>
+      <c r="K22">
+        <v>5.3732999986095817E-6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23">
+        <v>0.42566803097724909</v>
+      </c>
+      <c r="E23">
+        <v>7.536008208990097E-2</v>
+      </c>
+      <c r="F23">
+        <v>3.1029105186462399E-2</v>
+      </c>
+      <c r="G23">
+        <v>7.254909141920507E-4</v>
+      </c>
+      <c r="H23">
+        <v>6.3632898032665253E-2</v>
+      </c>
+      <c r="I23">
+        <v>0.40041515231132507</v>
+      </c>
+      <c r="J23">
+        <v>4.8265468329191208E-2</v>
+      </c>
+      <c r="K23">
+        <v>6.2892999994801361E-6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24">
+        <v>0.38332247734069819</v>
+      </c>
+      <c r="E24">
+        <v>7.6519288122653961E-2</v>
+      </c>
+      <c r="F24">
+        <v>2.3073434829711911E-2</v>
+      </c>
+      <c r="G24">
+        <v>2.3782176140230149E-4</v>
+      </c>
+      <c r="H24">
+        <v>6.1668548732995987E-2</v>
+      </c>
+      <c r="I24">
+        <v>0.4246203601360321</v>
+      </c>
+      <c r="J24">
+        <v>5.0253976136445999E-2</v>
+      </c>
+      <c r="K24">
+        <v>6.022100002155639E-6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25">
+        <v>0.25656527280807501</v>
+      </c>
+      <c r="E25">
+        <v>5.8768004179000848E-2</v>
+      </c>
+      <c r="F25">
+        <v>3.1726956367492683E-2</v>
+      </c>
+      <c r="G25">
+        <v>7.9306948464363813E-4</v>
+      </c>
+      <c r="H25">
+        <v>6.2162414193153381E-2</v>
+      </c>
+      <c r="I25">
+        <v>0.41348510980606079</v>
+      </c>
+      <c r="J25">
+        <v>4.7558601945638657E-2</v>
+      </c>
+      <c r="K25">
+        <v>6.1586000010720453E-6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26">
+        <v>0.2292059659957886</v>
+      </c>
+      <c r="E26">
+        <v>6.5167851746082306E-2</v>
+      </c>
+      <c r="F26">
+        <v>2.7948379516601559E-2</v>
+      </c>
+      <c r="G26">
+        <v>7.3515193071216345E-4</v>
+      </c>
+      <c r="H26">
+        <v>6.2986947596073151E-2</v>
+      </c>
+      <c r="I26">
+        <v>0.40807265043258673</v>
+      </c>
+      <c r="J26">
+        <v>4.7735970467329032E-2</v>
+      </c>
+      <c r="K26">
+        <v>5.6903999975475014E-6</v>
       </c>
     </row>
   </sheetData>
@@ -399,10 +1646,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5FE1693-6594-4531-B960-9EBF4152BAEA}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -423,6 +1676,893 @@
       </c>
       <c r="G1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2">
+        <v>0.10057032108306881</v>
+      </c>
+      <c r="E2">
+        <v>2.5618638843297958E-2</v>
+      </c>
+      <c r="F2">
+        <v>0.37667614221572882</v>
+      </c>
+      <c r="G2">
+        <v>3.2004408538341522E-2</v>
+      </c>
+      <c r="H2">
+        <v>0.96643120050430298</v>
+      </c>
+      <c r="I2">
+        <v>0.67498338222503662</v>
+      </c>
+      <c r="J2">
+        <v>0.30472478270530701</v>
+      </c>
+      <c r="K2">
+        <v>1.120819999778178E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3">
+        <v>0.1123339980840683</v>
+      </c>
+      <c r="E3">
+        <v>2.5978190824389461E-2</v>
+      </c>
+      <c r="F3">
+        <v>0.36365222930908198</v>
+      </c>
+      <c r="G3">
+        <v>3.0718173831701279E-2</v>
+      </c>
+      <c r="H3">
+        <v>0.96965622901916504</v>
+      </c>
+      <c r="I3">
+        <v>0.67883980274200439</v>
+      </c>
+      <c r="J3">
+        <v>0.31080695986747742</v>
+      </c>
+      <c r="K3">
+        <v>5.8958999979950016E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4">
+        <v>0.1082927286624908</v>
+      </c>
+      <c r="E4">
+        <v>2.531410567462444E-2</v>
+      </c>
+      <c r="F4">
+        <v>0.36998522281646729</v>
+      </c>
+      <c r="G4">
+        <v>3.1907930970191963E-2</v>
+      </c>
+      <c r="H4">
+        <v>0.13277177512645719</v>
+      </c>
+      <c r="I4">
+        <v>0.6800341010093689</v>
+      </c>
+      <c r="J4">
+        <v>0.30640903115272522</v>
+      </c>
+      <c r="K4">
+        <v>5.9803000003739728E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5">
+        <v>0.1196343451738358</v>
+      </c>
+      <c r="E5">
+        <v>2.5638896971940991E-2</v>
+      </c>
+      <c r="F5">
+        <v>0.36849296092987061</v>
+      </c>
+      <c r="G5">
+        <v>3.0902080237865451E-2</v>
+      </c>
+      <c r="H5">
+        <v>0.96911853551864624</v>
+      </c>
+      <c r="I5">
+        <v>0.67345398664474487</v>
+      </c>
+      <c r="J5">
+        <v>0.30846020579338068</v>
+      </c>
+      <c r="K5">
+        <v>5.7965000014519317E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6">
+        <v>0.117014154791832</v>
+      </c>
+      <c r="E6">
+        <v>2.5605883449316021E-2</v>
+      </c>
+      <c r="F6">
+        <v>0.38134282827377319</v>
+      </c>
+      <c r="G6">
+        <v>3.3014975488185883E-2</v>
+      </c>
+      <c r="H6">
+        <v>0.13578490912914279</v>
+      </c>
+      <c r="I6">
+        <v>0.68973380327224731</v>
+      </c>
+      <c r="J6">
+        <v>0.30266061425209051</v>
+      </c>
+      <c r="K6">
+        <v>5.2213999988452998E-6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7">
+        <v>37.790977478027337</v>
+      </c>
+      <c r="E7">
+        <v>3.034065723419189</v>
+      </c>
+      <c r="F7">
+        <v>959.11187744140625</v>
+      </c>
+      <c r="G7">
+        <v>8.0122642517089844</v>
+      </c>
+      <c r="H7">
+        <v>0.5832287073135376</v>
+      </c>
+      <c r="I7">
+        <v>0.45136845111846918</v>
+      </c>
+      <c r="J7">
+        <v>0.2876628041267395</v>
+      </c>
+      <c r="K7">
+        <v>6.7474999996193224E-6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8">
+        <v>38.448204040527337</v>
+      </c>
+      <c r="E8">
+        <v>3.03003978729248</v>
+      </c>
+      <c r="F8">
+        <v>951.85406494140625</v>
+      </c>
+      <c r="G8">
+        <v>8.1521139144897461</v>
+      </c>
+      <c r="H8">
+        <v>0.56269669532775879</v>
+      </c>
+      <c r="I8">
+        <v>0.45764708518981928</v>
+      </c>
+      <c r="J8">
+        <v>0.28140020370483398</v>
+      </c>
+      <c r="K8">
+        <v>6.2287999971886167E-6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9">
+        <v>38.159923553466797</v>
+      </c>
+      <c r="E9">
+        <v>3.0206947326660161</v>
+      </c>
+      <c r="F9">
+        <v>953.01409912109375</v>
+      </c>
+      <c r="G9">
+        <v>8.0963630676269531</v>
+      </c>
+      <c r="H9">
+        <v>0.56519407033920288</v>
+      </c>
+      <c r="I9">
+        <v>0.45782908797264099</v>
+      </c>
+      <c r="J9">
+        <v>0.2835347056388855</v>
+      </c>
+      <c r="K9">
+        <v>7.0119000010890876E-6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10">
+        <v>38.217014312744141</v>
+      </c>
+      <c r="E10">
+        <v>3.0109622478485112</v>
+      </c>
+      <c r="F10">
+        <v>955.25537109375</v>
+      </c>
+      <c r="G10">
+        <v>8.0810995101928711</v>
+      </c>
+      <c r="H10">
+        <v>0.56667524576187134</v>
+      </c>
+      <c r="I10">
+        <v>0.46334472298622131</v>
+      </c>
+      <c r="J10">
+        <v>0.28498271107673651</v>
+      </c>
+      <c r="K10">
+        <v>5.6958000022859782E-6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11">
+        <v>38.169883728027337</v>
+      </c>
+      <c r="E11">
+        <v>3.0170953273773189</v>
+      </c>
+      <c r="F11">
+        <v>945.50152587890625</v>
+      </c>
+      <c r="G11">
+        <v>8.0807600021362305</v>
+      </c>
+      <c r="H11">
+        <v>0.56254053115844727</v>
+      </c>
+      <c r="I11">
+        <v>0.45837205648422241</v>
+      </c>
+      <c r="J11">
+        <v>0.28487053513526922</v>
+      </c>
+      <c r="K11">
+        <v>5.2714000012201722E-6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12">
+        <v>39.317642211914063</v>
+      </c>
+      <c r="E12">
+        <v>2.9629571437835689</v>
+      </c>
+      <c r="F12">
+        <v>984.1077880859375</v>
+      </c>
+      <c r="G12">
+        <v>8.3264369964599609</v>
+      </c>
+      <c r="H12">
+        <v>0.53110146522521973</v>
+      </c>
+      <c r="I12">
+        <v>0.47578668594360352</v>
+      </c>
+      <c r="J12">
+        <v>0.3029690682888031</v>
+      </c>
+      <c r="K12">
+        <v>5.6876999988162416E-6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13">
+        <v>39.23785400390625</v>
+      </c>
+      <c r="E13">
+        <v>2.9632010459899898</v>
+      </c>
+      <c r="F13">
+        <v>980.4300537109375</v>
+      </c>
+      <c r="G13">
+        <v>8.3560504913330078</v>
+      </c>
+      <c r="H13">
+        <v>0.5334012508392334</v>
+      </c>
+      <c r="I13">
+        <v>0.47571873664855963</v>
+      </c>
+      <c r="J13">
+        <v>0.30732861161231989</v>
+      </c>
+      <c r="K13">
+        <v>5.6614000022818802E-6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14">
+        <v>39.483303070068359</v>
+      </c>
+      <c r="E14">
+        <v>2.9672625064849849</v>
+      </c>
+      <c r="F14">
+        <v>995.008544921875</v>
+      </c>
+      <c r="G14">
+        <v>8.4013071060180664</v>
+      </c>
+      <c r="H14">
+        <v>0.52973037958145142</v>
+      </c>
+      <c r="I14">
+        <v>0.47627308964729309</v>
+      </c>
+      <c r="J14">
+        <v>0.30593818426132202</v>
+      </c>
+      <c r="K14">
+        <v>5.2948000011383552E-6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15">
+        <v>39.129859924316413</v>
+      </c>
+      <c r="E15">
+        <v>2.958388090133667</v>
+      </c>
+      <c r="F15">
+        <v>980.79083251953125</v>
+      </c>
+      <c r="G15">
+        <v>8.2824869155883789</v>
+      </c>
+      <c r="H15">
+        <v>0.53416699171066284</v>
+      </c>
+      <c r="I15">
+        <v>0.47612851858139038</v>
+      </c>
+      <c r="J15">
+        <v>0.30586802959442139</v>
+      </c>
+      <c r="K15">
+        <v>5.5795000007492486E-6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16">
+        <v>39.221809387207031</v>
+      </c>
+      <c r="E16">
+        <v>2.9619226455688481</v>
+      </c>
+      <c r="F16">
+        <v>980.8865966796875</v>
+      </c>
+      <c r="G16">
+        <v>8.3276805877685547</v>
+      </c>
+      <c r="H16">
+        <v>0.53112512826919556</v>
+      </c>
+      <c r="I16">
+        <v>0.47523549199104309</v>
+      </c>
+      <c r="J16">
+        <v>0.30274829268455511</v>
+      </c>
+      <c r="K16">
+        <v>5.8175000012852249E-6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17">
+        <v>7.5142055749893188E-2</v>
+      </c>
+      <c r="E17">
+        <v>2.299807965755463E-2</v>
+      </c>
+      <c r="F17">
+        <v>5.0467252731323242E-3</v>
+      </c>
+      <c r="G17">
+        <v>1.5954678019625131E-5</v>
+      </c>
+      <c r="H17">
+        <v>5.4808832705020898E-2</v>
+      </c>
+      <c r="I17">
+        <v>0.47587025165557861</v>
+      </c>
+      <c r="J17">
+        <v>0.31497254967689509</v>
+      </c>
+      <c r="K17">
+        <v>9.663999997428619E-6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18">
+        <v>7.9901836812496185E-2</v>
+      </c>
+      <c r="E18">
+        <v>2.2972883656620979E-2</v>
+      </c>
+      <c r="F18">
+        <v>5.1014423370361328E-3</v>
+      </c>
+      <c r="G18">
+        <v>1.50457417475991E-5</v>
+      </c>
+      <c r="H18">
+        <v>5.4384905844926827E-2</v>
+      </c>
+      <c r="I18">
+        <v>0.47622844576835632</v>
+      </c>
+      <c r="J18">
+        <v>0.31412890553474432</v>
+      </c>
+      <c r="K18">
+        <v>8.2079999992856751E-6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19">
+        <v>7.4618488550186157E-2</v>
+      </c>
+      <c r="E19">
+        <v>2.3082828149199489E-2</v>
+      </c>
+      <c r="F19">
+        <v>4.9602985382080078E-3</v>
+      </c>
+      <c r="G19">
+        <v>1.6534580936422572E-5</v>
+      </c>
+      <c r="H19">
+        <v>5.5742092430591583E-2</v>
+      </c>
+      <c r="I19">
+        <v>0.47455108165740972</v>
+      </c>
+      <c r="J19">
+        <v>0.31175947189331049</v>
+      </c>
+      <c r="K19">
+        <v>7.8904000001784884E-6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20">
+        <v>7.3243372142314911E-2</v>
+      </c>
+      <c r="E20">
+        <v>2.3288313299417499E-2</v>
+      </c>
+      <c r="F20">
+        <v>4.9585103988647461E-3</v>
+      </c>
+      <c r="G20">
+        <v>1.652943319641054E-5</v>
+      </c>
+      <c r="H20">
+        <v>5.5199526250362403E-2</v>
+      </c>
+      <c r="I20">
+        <v>0.47527414560317988</v>
+      </c>
+      <c r="J20">
+        <v>0.31454584002494812</v>
+      </c>
+      <c r="K20">
+        <v>7.7401999988069296E-6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21">
+        <v>7.6334133744239807E-2</v>
+      </c>
+      <c r="E21">
+        <v>2.324997074902058E-2</v>
+      </c>
+      <c r="F21">
+        <v>5.1143169403076172E-3</v>
+      </c>
+      <c r="G21">
+        <v>1.5810088370926682E-5</v>
+      </c>
+      <c r="H21">
+        <v>5.4781448096036911E-2</v>
+      </c>
+      <c r="I21">
+        <v>0.47654464840888983</v>
+      </c>
+      <c r="J21">
+        <v>0.31277093291282648</v>
+      </c>
+      <c r="K21">
+        <v>7.4387000022397843E-6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22">
+        <v>1.2554029226303101</v>
+      </c>
+      <c r="E22">
+        <v>0.1131935641169548</v>
+      </c>
+      <c r="F22">
+        <v>3.1077861785888672E-3</v>
+      </c>
+      <c r="G22">
+        <v>4.6451496018562466E-6</v>
+      </c>
+      <c r="H22">
+        <v>4.1864827275276177E-2</v>
+      </c>
+      <c r="I22">
+        <v>1.054442882537842</v>
+      </c>
+      <c r="J22">
+        <v>0.27986875176429749</v>
+      </c>
+      <c r="K22">
+        <v>9.1148000028624661E-6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23">
+        <v>1.0228626728057859</v>
+      </c>
+      <c r="E23">
+        <v>0.15524290502071381</v>
+      </c>
+      <c r="F23">
+        <v>7.849574089050293E-3</v>
+      </c>
+      <c r="G23">
+        <v>3.0465816962532699E-5</v>
+      </c>
+      <c r="H23">
+        <v>5.2012529224157333E-2</v>
+      </c>
+      <c r="I23">
+        <v>1.031028628349304</v>
+      </c>
+      <c r="J23">
+        <v>0.29476305842399603</v>
+      </c>
+      <c r="K23">
+        <v>8.2626000003074301E-6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24">
+        <v>1.1495107412338259</v>
+      </c>
+      <c r="E24">
+        <v>0.1058946177363396</v>
+      </c>
+      <c r="F24">
+        <v>1.351070404052734E-2</v>
+      </c>
+      <c r="G24">
+        <v>3.6173842090647668E-5</v>
+      </c>
+      <c r="H24">
+        <v>5.8308474719524377E-2</v>
+      </c>
+      <c r="I24">
+        <v>1.061434745788574</v>
+      </c>
+      <c r="J24">
+        <v>0.30291110277175898</v>
+      </c>
+      <c r="K24">
+        <v>7.2626000001037028E-6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25">
+        <v>0.86765873432159424</v>
+      </c>
+      <c r="E25">
+        <v>9.6771173179149628E-2</v>
+      </c>
+      <c r="F25">
+        <v>2.1253824234008789E-2</v>
+      </c>
+      <c r="G25">
+        <v>6.5444015490356833E-5</v>
+      </c>
+      <c r="H25">
+        <v>6.5849274396896362E-2</v>
+      </c>
+      <c r="I25">
+        <v>0.97504997253417969</v>
+      </c>
+      <c r="J25">
+        <v>0.26940414309501648</v>
+      </c>
+      <c r="K25">
+        <v>7.9140999987430397E-6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26">
+        <v>0.88354760408401489</v>
+      </c>
+      <c r="E26">
+        <v>9.1126538813114166E-2</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>4.0527734905481339E-2</v>
+      </c>
+      <c r="I26">
+        <v>1.042904138565063</v>
+      </c>
+      <c r="J26">
+        <v>0.26883745193481451</v>
+      </c>
+      <c r="K26">
+        <v>8.1826999994518702E-6</v>
       </c>
     </row>
   </sheetData>
@@ -432,10 +2572,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4CC8EF-73B9-44EB-826D-9AA277E79EC2}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -456,6 +2602,893 @@
       </c>
       <c r="G1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2">
+        <v>0.96596360206604004</v>
+      </c>
+      <c r="E2">
+        <v>0.10429598391056059</v>
+      </c>
+      <c r="F2">
+        <v>17.984470367431641</v>
+      </c>
+      <c r="G2">
+        <v>8.3181120455265045E-2</v>
+      </c>
+      <c r="H2">
+        <v>0.19491951167583471</v>
+      </c>
+      <c r="I2">
+        <v>1.863996624946594</v>
+      </c>
+      <c r="J2">
+        <v>1.899414658546448</v>
+      </c>
+      <c r="K2">
+        <v>1.2257899998076031E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3">
+        <v>0.67883777618408203</v>
+      </c>
+      <c r="E3">
+        <v>0.10495872050523759</v>
+      </c>
+      <c r="F3">
+        <v>14.37751388549805</v>
+      </c>
+      <c r="G3">
+        <v>8.6362496018409729E-2</v>
+      </c>
+      <c r="H3">
+        <v>1.028795123100281</v>
+      </c>
+      <c r="I3">
+        <v>1.9283537864685061</v>
+      </c>
+      <c r="J3">
+        <v>2.0217196941375728</v>
+      </c>
+      <c r="K3">
+        <v>7.2804999981599404E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4">
+        <v>1.5724830627441411</v>
+      </c>
+      <c r="E4">
+        <v>0.13281574845314029</v>
+      </c>
+      <c r="F4">
+        <v>19.052274703979489</v>
+      </c>
+      <c r="G4">
+        <v>0.1076611801981926</v>
+      </c>
+      <c r="H4">
+        <v>0.9844127893447876</v>
+      </c>
+      <c r="I4">
+        <v>2.0737762451171879</v>
+      </c>
+      <c r="J4">
+        <v>2.2339344024658199</v>
+      </c>
+      <c r="K4">
+        <v>7.2857000013755167E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5">
+        <v>0.9875187873840332</v>
+      </c>
+      <c r="E5">
+        <v>0.1032232865691185</v>
+      </c>
+      <c r="F5">
+        <v>17.244873046875</v>
+      </c>
+      <c r="G5">
+        <v>7.7774226665496826E-2</v>
+      </c>
+      <c r="H5">
+        <v>1.0186194181442261</v>
+      </c>
+      <c r="I5">
+        <v>1.7820930480957029</v>
+      </c>
+      <c r="J5">
+        <v>1.8363533020019529</v>
+      </c>
+      <c r="K5">
+        <v>8.1175000013899995E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>0.99713635444641113</v>
+      </c>
+      <c r="E6">
+        <v>0.18277506530284879</v>
+      </c>
+      <c r="F6">
+        <v>24.746391296386719</v>
+      </c>
+      <c r="G6">
+        <v>0.1106208264827728</v>
+      </c>
+      <c r="H6">
+        <v>0.69618511199951172</v>
+      </c>
+      <c r="I6">
+        <v>2.2435276508331299</v>
+      </c>
+      <c r="J6">
+        <v>2.5342330932617192</v>
+      </c>
+      <c r="K6">
+        <v>7.5080999995407194E-6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7">
+        <v>86.036788940429688</v>
+      </c>
+      <c r="E7">
+        <v>4.7452383041381836</v>
+      </c>
+      <c r="F7">
+        <v>7468.8974609375</v>
+      </c>
+      <c r="G7">
+        <v>20.010736465454102</v>
+      </c>
+      <c r="H7">
+        <v>0.71990406513214111</v>
+      </c>
+      <c r="I7">
+        <v>1.4249463081359861</v>
+      </c>
+      <c r="J7">
+        <v>0.64628851413726807</v>
+      </c>
+      <c r="K7">
+        <v>7.7528000001620964E-6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8">
+        <v>84.781791687011719</v>
+      </c>
+      <c r="E8">
+        <v>4.714409351348877</v>
+      </c>
+      <c r="F8">
+        <v>7239.12109375</v>
+      </c>
+      <c r="G8">
+        <v>19.62985992431641</v>
+      </c>
+      <c r="H8">
+        <v>0.72203606367111206</v>
+      </c>
+      <c r="I8">
+        <v>1.4136315584182739</v>
+      </c>
+      <c r="J8">
+        <v>0.62908625602722168</v>
+      </c>
+      <c r="K8">
+        <v>7.9741999979887616E-6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9">
+        <v>85.073867797851563</v>
+      </c>
+      <c r="E9">
+        <v>4.7380843162536621</v>
+      </c>
+      <c r="F9">
+        <v>7324.83154296875</v>
+      </c>
+      <c r="G9">
+        <v>20.050027847290039</v>
+      </c>
+      <c r="H9">
+        <v>0.71811950206756592</v>
+      </c>
+      <c r="I9">
+        <v>1.425503730773926</v>
+      </c>
+      <c r="J9">
+        <v>0.65699928998947144</v>
+      </c>
+      <c r="K9">
+        <v>8.1682999989425296E-6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10">
+        <v>85.201942443847656</v>
+      </c>
+      <c r="E10">
+        <v>4.759157657623291</v>
+      </c>
+      <c r="F10">
+        <v>7317.763671875</v>
+      </c>
+      <c r="G10">
+        <v>19.777349472045898</v>
+      </c>
+      <c r="H10">
+        <v>0.71859478950500488</v>
+      </c>
+      <c r="I10">
+        <v>1.4227879047393801</v>
+      </c>
+      <c r="J10">
+        <v>0.62974578142166138</v>
+      </c>
+      <c r="K10">
+        <v>7.4886000002152283E-6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11">
+        <v>86.170005798339844</v>
+      </c>
+      <c r="E11">
+        <v>4.7479891777038574</v>
+      </c>
+      <c r="F11">
+        <v>7406.83642578125</v>
+      </c>
+      <c r="G11">
+        <v>19.70671272277832</v>
+      </c>
+      <c r="H11">
+        <v>0.71726638078689575</v>
+      </c>
+      <c r="I11">
+        <v>1.4271854162216191</v>
+      </c>
+      <c r="J11">
+        <v>0.61290627717971802</v>
+      </c>
+      <c r="K11">
+        <v>8.5441999981412661E-6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12">
+        <v>84.922492980957031</v>
+      </c>
+      <c r="E12">
+        <v>4.7176527976989746</v>
+      </c>
+      <c r="F12">
+        <v>7239.9765625</v>
+      </c>
+      <c r="G12">
+        <v>19.02021598815918</v>
+      </c>
+      <c r="H12">
+        <v>0.71944451332092285</v>
+      </c>
+      <c r="I12">
+        <v>1.528578639030457</v>
+      </c>
+      <c r="J12">
+        <v>0.67989307641983032</v>
+      </c>
+      <c r="K12">
+        <v>7.5817999968421646E-6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13">
+        <v>84.172767639160156</v>
+      </c>
+      <c r="E13">
+        <v>4.7105503082275391</v>
+      </c>
+      <c r="F13">
+        <v>7076.40576171875</v>
+      </c>
+      <c r="G13">
+        <v>19.030256271362301</v>
+      </c>
+      <c r="H13">
+        <v>0.71834850311279297</v>
+      </c>
+      <c r="I13">
+        <v>1.526430487632751</v>
+      </c>
+      <c r="J13">
+        <v>0.66474717855453491</v>
+      </c>
+      <c r="K13">
+        <v>7.8872999984014318E-6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14">
+        <v>81.891288757324219</v>
+      </c>
+      <c r="E14">
+        <v>4.687593936920166</v>
+      </c>
+      <c r="F14">
+        <v>6755.34130859375</v>
+      </c>
+      <c r="G14">
+        <v>18.756198883056641</v>
+      </c>
+      <c r="H14">
+        <v>0.71676421165466309</v>
+      </c>
+      <c r="I14">
+        <v>1.5192792415618901</v>
+      </c>
+      <c r="J14">
+        <v>0.69277524948120117</v>
+      </c>
+      <c r="K14">
+        <v>7.399699999950826E-6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15">
+        <v>85.082565307617188</v>
+      </c>
+      <c r="E15">
+        <v>4.6994256973266602</v>
+      </c>
+      <c r="F15">
+        <v>7261.630859375</v>
+      </c>
+      <c r="G15">
+        <v>19.188070297241211</v>
+      </c>
+      <c r="H15">
+        <v>0.71594280004501343</v>
+      </c>
+      <c r="I15">
+        <v>1.5280381441116331</v>
+      </c>
+      <c r="J15">
+        <v>0.67758023738861084</v>
+      </c>
+      <c r="K15">
+        <v>8.3965999983774967E-6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16">
+        <v>84.130752563476563</v>
+      </c>
+      <c r="E16">
+        <v>4.7039585113525391</v>
+      </c>
+      <c r="F16">
+        <v>7166.01904296875</v>
+      </c>
+      <c r="G16">
+        <v>19.135009765625</v>
+      </c>
+      <c r="H16">
+        <v>0.71655845642089844</v>
+      </c>
+      <c r="I16">
+        <v>1.526384115219116</v>
+      </c>
+      <c r="J16">
+        <v>0.69751912355422974</v>
+      </c>
+      <c r="K16">
+        <v>7.0889000016904906E-6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17">
+        <v>0.59529638290405273</v>
+      </c>
+      <c r="E17">
+        <v>4.8406973481178277E-2</v>
+      </c>
+      <c r="F17">
+        <v>0.65120697021484375</v>
+      </c>
+      <c r="G17">
+        <v>3.0862234416417778E-4</v>
+      </c>
+      <c r="H17">
+        <v>7.2306856513023376E-2</v>
+      </c>
+      <c r="I17">
+        <v>1.5226097106933589</v>
+      </c>
+      <c r="J17">
+        <v>0.82593560218811035</v>
+      </c>
+      <c r="K17">
+        <v>1.4661199998954541E-5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18">
+        <v>0.65451401472091675</v>
+      </c>
+      <c r="E18">
+        <v>5.3246546536684043E-2</v>
+      </c>
+      <c r="F18">
+        <v>0.82014083862304688</v>
+      </c>
+      <c r="G18">
+        <v>7.5689266668632627E-4</v>
+      </c>
+      <c r="H18">
+        <v>6.8549811840057373E-2</v>
+      </c>
+      <c r="I18">
+        <v>1.5131886005401609</v>
+      </c>
+      <c r="J18">
+        <v>0.76921224594116211</v>
+      </c>
+      <c r="K18">
+        <v>1.415869999982533E-5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19">
+        <v>0.58106464147567749</v>
+      </c>
+      <c r="E19">
+        <v>4.9415320158004761E-2</v>
+      </c>
+      <c r="F19">
+        <v>0.68774032592773438</v>
+      </c>
+      <c r="G19">
+        <v>7.7934941509738564E-4</v>
+      </c>
+      <c r="H19">
+        <v>6.9682404398918152E-2</v>
+      </c>
+      <c r="I19">
+        <v>1.523853063583374</v>
+      </c>
+      <c r="J19">
+        <v>0.76091235876083374</v>
+      </c>
+      <c r="K19">
+        <v>1.6437799997220279E-5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20">
+        <v>0.68824237585067749</v>
+      </c>
+      <c r="E20">
+        <v>4.9762345850467682E-2</v>
+      </c>
+      <c r="F20">
+        <v>0.43884658813476563</v>
+      </c>
+      <c r="G20">
+        <v>2.1226776880212131E-4</v>
+      </c>
+      <c r="H20">
+        <v>7.2582662105560303E-2</v>
+      </c>
+      <c r="I20">
+        <v>1.5455590486526489</v>
+      </c>
+      <c r="J20">
+        <v>0.82611113786697388</v>
+      </c>
+      <c r="K20">
+        <v>1.8171700001403219E-5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21">
+        <v>0.60902684926986694</v>
+      </c>
+      <c r="E21">
+        <v>5.173289030790329E-2</v>
+      </c>
+      <c r="F21">
+        <v>0.88250732421875</v>
+      </c>
+      <c r="G21">
+        <v>5.2995694568380713E-4</v>
+      </c>
+      <c r="H21">
+        <v>6.9696880877017975E-2</v>
+      </c>
+      <c r="I21">
+        <v>1.529053688049316</v>
+      </c>
+      <c r="J21">
+        <v>0.77638143301010132</v>
+      </c>
+      <c r="K21">
+        <v>1.3562100000854119E-5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22">
+        <v>1.4329888820648189</v>
+      </c>
+      <c r="E22">
+        <v>4.1691161692142487E-2</v>
+      </c>
+      <c r="F22">
+        <v>0.36400866508483892</v>
+      </c>
+      <c r="G22">
+        <v>1.154186757048592E-4</v>
+      </c>
+      <c r="H22">
+        <v>4.5522239059209817E-2</v>
+      </c>
+      <c r="I22">
+        <v>0.95341664552688599</v>
+      </c>
+      <c r="J22">
+        <v>0.63750797510147095</v>
+      </c>
+      <c r="K22">
+        <v>1.3498599997546991E-5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23">
+        <v>1.532139778137207</v>
+      </c>
+      <c r="E23">
+        <v>4.2914818972349167E-2</v>
+      </c>
+      <c r="F23">
+        <v>0.43060636520385742</v>
+      </c>
+      <c r="G23">
+        <v>1.1407135025365279E-4</v>
+      </c>
+      <c r="H23">
+        <v>5.0512645393610001E-2</v>
+      </c>
+      <c r="I23">
+        <v>1.0042508840560911</v>
+      </c>
+      <c r="J23">
+        <v>0.65910685062408447</v>
+      </c>
+      <c r="K23">
+        <v>1.4727300000231479E-5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24">
+        <v>1.460663795471191</v>
+      </c>
+      <c r="E24">
+        <v>4.401947557926178E-2</v>
+      </c>
+      <c r="F24">
+        <v>0.1893651485443115</v>
+      </c>
+      <c r="G24">
+        <v>4.1196653910446912E-5</v>
+      </c>
+      <c r="H24">
+        <v>5.1034536212682717E-2</v>
+      </c>
+      <c r="I24">
+        <v>1.03366482257843</v>
+      </c>
+      <c r="J24">
+        <v>0.63442659378051758</v>
+      </c>
+      <c r="K24">
+        <v>1.5350300000136489E-5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" t="s">
+        <v>119</v>
+      </c>
+      <c r="D25">
+        <v>1.5647110939025879</v>
+      </c>
+      <c r="E25">
+        <v>4.1086908429861069E-2</v>
+      </c>
+      <c r="F25">
+        <v>0.28982746601104742</v>
+      </c>
+      <c r="G25">
+        <v>6.1307444411795586E-5</v>
+      </c>
+      <c r="H25">
+        <v>4.9035333096981049E-2</v>
+      </c>
+      <c r="I25">
+        <v>0.89492589235305786</v>
+      </c>
+      <c r="J25">
+        <v>0.70326727628707886</v>
+      </c>
+      <c r="K25">
+        <v>1.3406699999904959E-5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26">
+        <v>1.395487308502197</v>
+      </c>
+      <c r="E26">
+        <v>4.4395580887794488E-2</v>
+      </c>
+      <c r="F26">
+        <v>0.37094831466674799</v>
+      </c>
+      <c r="G26">
+        <v>5.7352586736669757E-5</v>
+      </c>
+      <c r="H26">
+        <v>5.1778201013803482E-2</v>
+      </c>
+      <c r="I26">
+        <v>0.95604383945465088</v>
+      </c>
+      <c r="J26">
+        <v>0.7030646800994873</v>
+      </c>
+      <c r="K26">
+        <v>1.47992999991402E-5</v>
       </c>
     </row>
   </sheetData>
@@ -465,19 +3498,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B6C0182-E21B-4C9D-A3D8-55CCC8C77B4F}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,6 +3528,893 @@
       </c>
       <c r="G1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2">
+        <v>23.63044548034668</v>
+      </c>
+      <c r="E2">
+        <v>0.98168623447418213</v>
+      </c>
+      <c r="F2">
+        <v>0.876578688621521</v>
+      </c>
+      <c r="G2">
+        <v>3.6645263433456421E-2</v>
+      </c>
+      <c r="H2">
+        <v>1.03788697719574</v>
+      </c>
+      <c r="I2">
+        <v>7.9258160591125488</v>
+      </c>
+      <c r="J2">
+        <v>0.45246326923370361</v>
+      </c>
+      <c r="K2">
+        <v>1.523850000012317E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3">
+        <v>23.61324310302734</v>
+      </c>
+      <c r="E3">
+        <v>1.0098352432250981</v>
+      </c>
+      <c r="F3">
+        <v>0.87675732374191284</v>
+      </c>
+      <c r="G3">
+        <v>3.7452258169651031E-2</v>
+      </c>
+      <c r="H3">
+        <v>0.57337284088134766</v>
+      </c>
+      <c r="I3">
+        <v>8.1449546813964844</v>
+      </c>
+      <c r="J3">
+        <v>0.43518039584159851</v>
+      </c>
+      <c r="K3">
+        <v>9.8455999977886674E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4">
+        <v>23.6240234375</v>
+      </c>
+      <c r="E4">
+        <v>1.047832250595093</v>
+      </c>
+      <c r="F4">
+        <v>0.86388081312179565</v>
+      </c>
+      <c r="G4">
+        <v>3.9059147238731377E-2</v>
+      </c>
+      <c r="H4">
+        <v>0.74506008625030518</v>
+      </c>
+      <c r="I4">
+        <v>8.2632608413696289</v>
+      </c>
+      <c r="J4">
+        <v>0.44792824983596802</v>
+      </c>
+      <c r="K4">
+        <v>1.0181300000112971E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5">
+        <v>23.60359954833984</v>
+      </c>
+      <c r="E5">
+        <v>0.99049592018127441</v>
+      </c>
+      <c r="F5">
+        <v>0.88359981775283813</v>
+      </c>
+      <c r="G5">
+        <v>4.2049899697303772E-2</v>
+      </c>
+      <c r="H5">
+        <v>0.98637479543685913</v>
+      </c>
+      <c r="I5">
+        <v>7.9121212959289551</v>
+      </c>
+      <c r="J5">
+        <v>0.46530181169509888</v>
+      </c>
+      <c r="K5">
+        <v>1.05130999982066E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6">
+        <v>23.60688591003418</v>
+      </c>
+      <c r="E6">
+        <v>0.99238467216491699</v>
+      </c>
+      <c r="F6">
+        <v>0.87961739301681519</v>
+      </c>
+      <c r="G6">
+        <v>3.7383366376161582E-2</v>
+      </c>
+      <c r="H6">
+        <v>0.80943077802658081</v>
+      </c>
+      <c r="I6">
+        <v>7.9993424415588379</v>
+      </c>
+      <c r="J6">
+        <v>0.44606921076774603</v>
+      </c>
+      <c r="K6">
+        <v>1.009359999807202E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7">
+        <v>305.21298217773438</v>
+      </c>
+      <c r="E7">
+        <v>10.863534927368161</v>
+      </c>
+      <c r="F7">
+        <v>76053.8984375</v>
+      </c>
+      <c r="G7">
+        <v>47.887935638427727</v>
+      </c>
+      <c r="H7">
+        <v>0.58295440673828125</v>
+      </c>
+      <c r="I7">
+        <v>8.1716432571411133</v>
+      </c>
+      <c r="J7">
+        <v>0.4901336133480072</v>
+      </c>
+      <c r="K7">
+        <v>1.026329999876907E-5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8">
+        <v>300.15142822265619</v>
+      </c>
+      <c r="E8">
+        <v>10.81852340698242</v>
+      </c>
+      <c r="F8">
+        <v>73560.59375</v>
+      </c>
+      <c r="G8">
+        <v>44.449806213378913</v>
+      </c>
+      <c r="H8">
+        <v>0.58302116394042969</v>
+      </c>
+      <c r="I8">
+        <v>8.2421140670776367</v>
+      </c>
+      <c r="J8">
+        <v>0.49444201588630682</v>
+      </c>
+      <c r="K8">
+        <v>9.8615999995672616E-6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9">
+        <v>297.33950805664063</v>
+      </c>
+      <c r="E9">
+        <v>10.816483497619631</v>
+      </c>
+      <c r="F9">
+        <v>72244.734375</v>
+      </c>
+      <c r="G9">
+        <v>44.344440460205078</v>
+      </c>
+      <c r="H9">
+        <v>0.58412820100784302</v>
+      </c>
+      <c r="I9">
+        <v>8.2302160263061523</v>
+      </c>
+      <c r="J9">
+        <v>0.49271392822265619</v>
+      </c>
+      <c r="K9">
+        <v>9.8335999973642166E-6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10">
+        <v>301.57559204101563</v>
+      </c>
+      <c r="E10">
+        <v>10.844674110412599</v>
+      </c>
+      <c r="F10">
+        <v>74250.671875</v>
+      </c>
+      <c r="G10">
+        <v>45.354511260986328</v>
+      </c>
+      <c r="H10">
+        <v>0.58105278015136719</v>
+      </c>
+      <c r="I10">
+        <v>8.2295856475830078</v>
+      </c>
+      <c r="J10">
+        <v>0.496104896068573</v>
+      </c>
+      <c r="K10">
+        <v>9.8043999969377189E-6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11">
+        <v>301.6357421875</v>
+      </c>
+      <c r="E11">
+        <v>10.8266487121582</v>
+      </c>
+      <c r="F11">
+        <v>74250.3359375</v>
+      </c>
+      <c r="G11">
+        <v>45.375465393066413</v>
+      </c>
+      <c r="H11">
+        <v>0.58175790309906006</v>
+      </c>
+      <c r="I11">
+        <v>8.2327127456665039</v>
+      </c>
+      <c r="J11">
+        <v>0.49149990081787109</v>
+      </c>
+      <c r="K11">
+        <v>1.0026400002971061E-5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12">
+        <v>310.95364379882813</v>
+      </c>
+      <c r="E12">
+        <v>10.877345085144039</v>
+      </c>
+      <c r="F12">
+        <v>78727.03125</v>
+      </c>
+      <c r="G12">
+        <v>49.688991546630859</v>
+      </c>
+      <c r="H12">
+        <v>0.57971078157424927</v>
+      </c>
+      <c r="I12">
+        <v>8.019648551940918</v>
+      </c>
+      <c r="J12">
+        <v>0.49313586950302118</v>
+      </c>
+      <c r="K12">
+        <v>9.6345999991171994E-6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13">
+        <v>313.78646850585938</v>
+      </c>
+      <c r="E13">
+        <v>10.84992790222168</v>
+      </c>
+      <c r="F13">
+        <v>79825.828125</v>
+      </c>
+      <c r="G13">
+        <v>51.642375946044922</v>
+      </c>
+      <c r="H13">
+        <v>0.57631927728652954</v>
+      </c>
+      <c r="I13">
+        <v>8.0604658126831055</v>
+      </c>
+      <c r="J13">
+        <v>0.49374780058860779</v>
+      </c>
+      <c r="K13">
+        <v>1.048179999997956E-5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14">
+        <v>309.83099365234381</v>
+      </c>
+      <c r="E14">
+        <v>10.907889366149901</v>
+      </c>
+      <c r="F14">
+        <v>78250.234375</v>
+      </c>
+      <c r="G14">
+        <v>48.187713623046882</v>
+      </c>
+      <c r="H14">
+        <v>0.57970476150512695</v>
+      </c>
+      <c r="I14">
+        <v>8.0690078735351563</v>
+      </c>
+      <c r="J14">
+        <v>0.49643966555595398</v>
+      </c>
+      <c r="K14">
+        <v>9.7451999972690822E-6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15">
+        <v>312.12847900390619</v>
+      </c>
+      <c r="E15">
+        <v>10.81918334960938</v>
+      </c>
+      <c r="F15">
+        <v>79110.859375</v>
+      </c>
+      <c r="G15">
+        <v>50.724849700927727</v>
+      </c>
+      <c r="H15">
+        <v>0.5783921480178833</v>
+      </c>
+      <c r="I15">
+        <v>8.1053695678710938</v>
+      </c>
+      <c r="J15">
+        <v>0.49543377757072449</v>
+      </c>
+      <c r="K15">
+        <v>1.032560000021476E-5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16">
+        <v>312.30996704101563</v>
+      </c>
+      <c r="E16">
+        <v>10.86781215667725</v>
+      </c>
+      <c r="F16">
+        <v>79263.625</v>
+      </c>
+      <c r="G16">
+        <v>50.273677825927727</v>
+      </c>
+      <c r="H16">
+        <v>0.57750678062438965</v>
+      </c>
+      <c r="I16">
+        <v>8.0384387969970703</v>
+      </c>
+      <c r="J16">
+        <v>0.49570822715759277</v>
+      </c>
+      <c r="K16">
+        <v>1.0809300001710651E-5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17">
+        <v>23.641475677490231</v>
+      </c>
+      <c r="E17">
+        <v>0.99417406320571899</v>
+      </c>
+      <c r="F17">
+        <v>5.2222251892089837E-2</v>
+      </c>
+      <c r="G17">
+        <v>3.1380006112158298E-4</v>
+      </c>
+      <c r="H17">
+        <v>0.16459585726261139</v>
+      </c>
+      <c r="I17">
+        <v>8.1236228942871094</v>
+      </c>
+      <c r="J17">
+        <v>0.46110212802886957</v>
+      </c>
+      <c r="K17">
+        <v>2.2302900000795489E-5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18">
+        <v>23.634784698486332</v>
+      </c>
+      <c r="E18">
+        <v>1.002053380012512</v>
+      </c>
+      <c r="F18">
+        <v>4.7666072845458977E-2</v>
+      </c>
+      <c r="G18">
+        <v>1.3933748414274311E-4</v>
+      </c>
+      <c r="H18">
+        <v>0.1567940562963486</v>
+      </c>
+      <c r="I18">
+        <v>8.1748495101928711</v>
+      </c>
+      <c r="J18">
+        <v>0.49669966101646418</v>
+      </c>
+      <c r="K18">
+        <v>2.3180300002422879E-5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19">
+        <v>23.637508392333981</v>
+      </c>
+      <c r="E19">
+        <v>0.9937584400177002</v>
+      </c>
+      <c r="F19">
+        <v>5.3722977638244629E-2</v>
+      </c>
+      <c r="G19">
+        <v>3.3510313369333739E-4</v>
+      </c>
+      <c r="H19">
+        <v>0.16388283669948581</v>
+      </c>
+      <c r="I19">
+        <v>8.0634651184082031</v>
+      </c>
+      <c r="J19">
+        <v>0.46835106611251831</v>
+      </c>
+      <c r="K19">
+        <v>2.280270000119344E-5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20">
+        <v>23.537300109863281</v>
+      </c>
+      <c r="E20">
+        <v>0.99885892868041992</v>
+      </c>
+      <c r="F20">
+        <v>2.712249755859375E-2</v>
+      </c>
+      <c r="G20">
+        <v>4.438744144863449E-5</v>
+      </c>
+      <c r="H20">
+        <v>0.15479184687137601</v>
+      </c>
+      <c r="I20">
+        <v>8.1400938034057617</v>
+      </c>
+      <c r="J20">
+        <v>0.57704383134841919</v>
+      </c>
+      <c r="K20">
+        <v>2.4676900000486059E-5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21">
+        <v>23.640838623046879</v>
+      </c>
+      <c r="E21">
+        <v>1.0012080669403081</v>
+      </c>
+      <c r="F21">
+        <v>5.245053768157959E-2</v>
+      </c>
+      <c r="G21">
+        <v>3.2466347329318518E-4</v>
+      </c>
+      <c r="H21">
+        <v>0.16431500017642969</v>
+      </c>
+      <c r="I21">
+        <v>8.0990362167358398</v>
+      </c>
+      <c r="J21">
+        <v>0.46192082762718201</v>
+      </c>
+      <c r="K21">
+        <v>2.5207999999111049E-5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22">
+        <v>23.81794548034668</v>
+      </c>
+      <c r="E22">
+        <v>1.52560818195343</v>
+      </c>
+      <c r="F22">
+        <v>8.4075689315795898E-2</v>
+      </c>
+      <c r="G22">
+        <v>2.366854023421183E-4</v>
+      </c>
+      <c r="H22">
+        <v>0.15575078129768369</v>
+      </c>
+      <c r="I22">
+        <v>14.28986644744873</v>
+      </c>
+      <c r="J22">
+        <v>0.70168322324752808</v>
+      </c>
+      <c r="K22">
+        <v>2.2148799998831241E-5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23">
+        <v>23.537607192993161</v>
+      </c>
+      <c r="E23">
+        <v>1.556927442550659</v>
+      </c>
+      <c r="F23">
+        <v>3.9977788925170898E-2</v>
+      </c>
+      <c r="G23">
+        <v>5.1726590754697099E-5</v>
+      </c>
+      <c r="H23">
+        <v>0.15351104736328119</v>
+      </c>
+      <c r="I23">
+        <v>14.24219417572021</v>
+      </c>
+      <c r="J23">
+        <v>0.69089812040328979</v>
+      </c>
+      <c r="K23">
+        <v>2.4780700001429071E-5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24">
+        <v>23.450736999511719</v>
+      </c>
+      <c r="E24">
+        <v>1.541547894477844</v>
+      </c>
+      <c r="F24">
+        <v>3.8616657257080078E-2</v>
+      </c>
+      <c r="G24">
+        <v>8.1535363278817385E-5</v>
+      </c>
+      <c r="H24">
+        <v>0.1589006781578064</v>
+      </c>
+      <c r="I24">
+        <v>14.130941390991209</v>
+      </c>
+      <c r="J24">
+        <v>0.68010294437408447</v>
+      </c>
+      <c r="K24">
+        <v>2.5538400001096311E-5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25">
+        <v>23.57296180725098</v>
+      </c>
+      <c r="E25">
+        <v>1.554420590400696</v>
+      </c>
+      <c r="F25">
+        <v>3.5624980926513672E-2</v>
+      </c>
+      <c r="G25">
+        <v>6.1847953475080431E-5</v>
+      </c>
+      <c r="H25">
+        <v>0.15143682062625891</v>
+      </c>
+      <c r="I25">
+        <v>14.18090915679932</v>
+      </c>
+      <c r="J25">
+        <v>0.68167054653167725</v>
+      </c>
+      <c r="K25">
+        <v>2.329570000074455E-5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" t="s">
+        <v>95</v>
+      </c>
+      <c r="D26">
+        <v>23.467864990234379</v>
+      </c>
+      <c r="E26">
+        <v>1.5504075288772581</v>
+      </c>
+      <c r="F26">
+        <v>4.247593879699707E-2</v>
+      </c>
+      <c r="G26">
+        <v>5.1088340114802122E-5</v>
+      </c>
+      <c r="H26">
+        <v>0.1514802873134613</v>
+      </c>
+      <c r="I26">
+        <v>14.17725944519043</v>
+      </c>
+      <c r="J26">
+        <v>0.70202308893203735</v>
+      </c>
+      <c r="K26">
+        <v>2.38418000008096E-5</v>
       </c>
     </row>
   </sheetData>
